--- a/sheets/조재수대금교본/검수/장윤정 송인.xlsx
+++ b/sheets/조재수대금교본/검수/장윤정 송인.xlsx
@@ -4485,11 +4485,7 @@
         </is>
       </c>
       <c r="G5" s="24"/>
-      <c r="H5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="H5" s="21"/>
       <c r="I5" s="24"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
@@ -4642,51 +4638,44 @@
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
-‹</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="C8" s="24"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-‹</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="G8" s="24"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-ﾉ</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I8" s="24"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-林
-‹</t>
+林</t>
         </is>
       </c>
       <c r="K8" s="24"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-‹</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="M8" s="24"/>
       <c r="N8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="O8" s="24"/>
@@ -4699,8 +4688,7 @@
       <c r="Q8" s="24"/>
       <c r="R8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
-‹</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="S8" s="24"/>
@@ -4895,21 +4883,13 @@
       <c r="E13" s="23"/>
       <c r="F13" s="21"/>
       <c r="G13" s="23"/>
-      <c r="H13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H13" s="21"/>
       <c r="I13" s="23"/>
       <c r="J13" s="21"/>
       <c r="K13" s="23"/>
       <c r="L13" s="21"/>
       <c r="M13" s="23"/>
-      <c r="N13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N13" s="21"/>
       <c r="O13" s="23"/>
       <c r="P13" s="21"/>
       <c r="Q13" s="23"/>
@@ -4918,11 +4898,7 @@
     </row>
     <row r="14" ht="96.05" customHeight="true">
       <c r="A14" s="0"/>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B14" s="21"/>
       <c r="C14" s="24"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
@@ -4943,11 +4919,7 @@
         </is>
       </c>
       <c r="I14" s="24"/>
-      <c r="J14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J14" s="21"/>
       <c r="K14" s="24"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
@@ -4968,11 +4940,7 @@
         </is>
       </c>
       <c r="Q14" s="24"/>
-      <c r="R14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R14" s="21"/>
       <c r="S14" s="24"/>
     </row>
     <row r="15" ht="6.0" customHeight="true">
@@ -5019,13 +4987,13 @@
       <c r="M17" s="22"/>
       <c r="N17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰ㄷ</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="O17" s="22"/>
       <c r="P17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰ㄷ</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="Q17" s="22"/>
@@ -5078,8 +5046,7 @@
       <c r="M19" s="24"/>
       <c r="N19" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-‹</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="O19" s="24"/>
@@ -5108,7 +5075,7 @@
       <c r="M20" s="22"/>
       <c r="N20" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄱ</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="O20" s="22"/>
@@ -5173,23 +5140,20 @@
       <c r="N22" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-㳞
-‹</t>
+㳞</t>
         </is>
       </c>
       <c r="O22" s="24"/>
       <c r="P22" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="Q22" s="24"/>
       <c r="R22" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-林
-‹</t>
+林</t>
         </is>
       </c>
       <c r="S22" s="24"/>
@@ -5345,17 +5309,9 @@
         </is>
       </c>
       <c r="O28" s="24"/>
-      <c r="P28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P28" s="21"/>
       <c r="Q28" s="24"/>
-      <c r="R28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R28" s="21"/>
       <c r="S28" s="24"/>
     </row>
   </sheetData>

--- a/sheets/조재수대금교본/검수/장윤정 송인.xlsx
+++ b/sheets/조재수대금교본/검수/장윤정 송인.xlsx
@@ -4485,7 +4485,11 @@
         </is>
       </c>
       <c r="G5" s="24"/>
-      <c r="H5" s="21"/>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="I5" s="24"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
@@ -4656,7 +4660,8 @@
       <c r="G8" s="24"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢
+ﾉ</t>
         </is>
       </c>
       <c r="I8" s="24"/>
@@ -4987,13 +4992,13 @@
       <c r="M17" s="22"/>
       <c r="N17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰ㄷ</t>
         </is>
       </c>
       <c r="O17" s="22"/>
       <c r="P17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰ㄷ</t>
         </is>
       </c>
       <c r="Q17" s="22"/>
@@ -5075,7 +5080,7 @@
       <c r="M20" s="22"/>
       <c r="N20" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳ㄱ</t>
         </is>
       </c>
       <c r="O20" s="22"/>

--- a/sheets/조재수대금교본/검수/장윤정 송인.xlsx
+++ b/sheets/조재수대금교본/검수/장윤정 송인.xlsx
@@ -4306,30 +4306,30 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="64.52" customHeight="true">
+    <row r="2" ht="71.43" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
     </row>
-    <row r="3" ht="96.05" customHeight="true">
+    <row r="3" ht="106.4" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="S3" s="22"/>
     </row>
-    <row r="4" ht="96.05" customHeight="true">
+    <row r="4" ht="106.4" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="S4" s="23"/>
     </row>
-    <row r="5" ht="96.05" customHeight="true">
+    <row r="5" ht="106.4" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="24"/>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="S5" s="24"/>
     </row>
-    <row r="6" ht="96.05" customHeight="true">
+    <row r="6" ht="106.4" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21"/>
       <c r="C6" s="22"/>
@@ -4577,7 +4577,7 @@
       </c>
       <c r="S6" s="22"/>
     </row>
-    <row r="7" ht="96.05" customHeight="true">
+    <row r="7" ht="106.4" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="23"/>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="S7" s="23"/>
     </row>
-    <row r="8" ht="96.05" customHeight="true">
+    <row r="8" ht="106.4" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="S8" s="24"/>
     </row>
-    <row r="9" ht="96.05" customHeight="true">
+    <row r="9" ht="106.4" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="S9" s="22"/>
     </row>
-    <row r="10" ht="96.05" customHeight="true">
+    <row r="10" ht="106.4" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="23"/>
@@ -4797,7 +4797,7 @@
       </c>
       <c r="S10" s="23"/>
     </row>
-    <row r="11" ht="96.05" customHeight="true">
+    <row r="11" ht="106.4" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="24"/>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="S11" s="24"/>
     </row>
-    <row r="12" ht="96.05" customHeight="true">
+    <row r="12" ht="106.4" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="S12" s="22"/>
     </row>
-    <row r="13" ht="96.05" customHeight="true">
+    <row r="13" ht="106.4" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -4901,7 +4901,7 @@
       <c r="R13" s="21"/>
       <c r="S13" s="23"/>
     </row>
-    <row r="14" ht="96.05" customHeight="true">
+    <row r="14" ht="106.4" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>
@@ -4951,7 +4951,7 @@
     <row r="15" ht="6.0" customHeight="true">
       <c r="A15" s="0"/>
     </row>
-    <row r="16" ht="64.52" customHeight="true">
+    <row r="16" ht="71.43" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
       <c r="R16" s="20"/>
       <c r="S16" s="20"/>
     </row>
-    <row r="17" ht="96.05" customHeight="true">
+    <row r="17" ht="106.4" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="22"/>
@@ -5009,7 +5009,7 @@
       </c>
       <c r="S17" s="22"/>
     </row>
-    <row r="18" ht="96.05" customHeight="true">
+    <row r="18" ht="106.4" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="23"/>
@@ -5035,7 +5035,7 @@
       </c>
       <c r="S18" s="23"/>
     </row>
-    <row r="19" ht="96.05" customHeight="true">
+    <row r="19" ht="106.4" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="24"/>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="S19" s="24"/>
     </row>
-    <row r="20" ht="96.05" customHeight="true">
+    <row r="20" ht="106.4" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="22"/>
@@ -5097,7 +5097,7 @@
       </c>
       <c r="S20" s="22"/>
     </row>
-    <row r="21" ht="96.05" customHeight="true">
+    <row r="21" ht="106.4" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="23"/>
@@ -5128,7 +5128,7 @@
       </c>
       <c r="S21" s="23"/>
     </row>
-    <row r="22" ht="96.05" customHeight="true">
+    <row r="22" ht="106.4" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="24"/>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="S22" s="24"/>
     </row>
-    <row r="23" ht="96.05" customHeight="true">
+    <row r="23" ht="106.4" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="22"/>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="S23" s="22"/>
     </row>
-    <row r="24" ht="96.05" customHeight="true">
+    <row r="24" ht="106.4" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="23"/>
@@ -5222,7 +5222,7 @@
       <c r="R24" s="21"/>
       <c r="S24" s="23"/>
     </row>
-    <row r="25" ht="96.05" customHeight="true">
+    <row r="25" ht="106.4" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="24"/>
@@ -5248,7 +5248,7 @@
       <c r="R25" s="21"/>
       <c r="S25" s="24"/>
     </row>
-    <row r="26" ht="96.05" customHeight="true">
+    <row r="26" ht="106.4" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="22"/>
@@ -5273,7 +5273,7 @@
       <c r="R26" s="21"/>
       <c r="S26" s="22"/>
     </row>
-    <row r="27" ht="96.05" customHeight="true">
+    <row r="27" ht="106.4" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="23"/>
@@ -5294,7 +5294,7 @@
       <c r="R27" s="21"/>
       <c r="S27" s="23"/>
     </row>
-    <row r="28" ht="96.05" customHeight="true">
+    <row r="28" ht="106.4" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21"/>
       <c r="C28" s="24"/>
@@ -5326,7 +5326,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="56"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="14" max="16383" man="1"/>
   </rowBreaks>
